--- a/I_dijkastra/graficas.xlsx
+++ b/I_dijkastra/graficas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\posgrado\analisis_algoritmos\I_dijkastra\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58A1A497-758A-44B5-A555-B1F9D4C9EA68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FA6CE4D-5CC9-41BB-BB91-FA223CE4E0BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2662,16 +2662,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>121920</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>95026</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>34514</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>426720</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>399826</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>34514</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
